--- a/data/output/evaluasi_63.xlsx
+++ b/data/output/evaluasi_63.xlsx
@@ -8,8 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="6300" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="6306" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="6304" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6304" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6308" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6301" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6303" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6305" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6306" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="6307" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6309" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="6310" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="6311" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="6371" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="6372" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,6 +437,686 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provinsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.777180222452156</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>63</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.882413850736679</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q2-25 vs q-to-q_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.130815919935781</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-35.06104730202193</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>35.80834866828056</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8792323792872435</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.17601380570649</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.486541026006893</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.070300340852527</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>63</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.397753143535639</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>63</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.17601380570649</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>63</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.486541026006893</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>63</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.035119420821042</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.06669035461002081</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25 vs implisit_q-to-q_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>63</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.820005181915199</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q2-25 vs implisit_y-on-y_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>63</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4.141059239970073</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.943410645090137</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.511408720245001</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.40668336224653</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1293638241706381</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6310</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1055824827864165</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -438,7 +1128,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>provinsi</t>
+          <t>kabupaten/kota</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -464,85 +1154,289 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63</v>
+        <v>6311</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kalimantan Selatan</t>
+          <t>Kabupaten Balangan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.02849385420091438</v>
+        <v>-2.446123540978345</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63</v>
+        <v>6311</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kalimantan Selatan</t>
+          <t>Kabupaten Balangan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2964709971689647</v>
+        <v>-3.866787624015916</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63</v>
+        <v>6311</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kalimantan Selatan</t>
+          <t>Kabupaten Balangan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.679159071966613</v>
+        <v>-0.7058408607204564</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-6.347877433014143</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.831894599824232</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6371</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.8960224649125561</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6372</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.54202524814951</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -557,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,85 +1488,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6306</v>
+        <v>6304</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Hulu Sungai Selatan</t>
+          <t>Kabupaten Barito Kuala</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1756397558457677</v>
+        <v>-0.02405970998291913</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25_ril vs q-to-q_pkrt_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q2-25_ril vs implisit_q-to-q_pkrt_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6306</v>
+        <v>6304</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Hulu Sungai Selatan</t>
+          <t>Kabupaten Barito Kuala</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.1341261933310383</v>
+        <v>40.73934117089822</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6306</v>
+        <v>6304</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Hulu Sungai Selatan</t>
+          <t>Kabupaten Barito Kuala</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1212845515709668</v>
+        <v>-0.6164444145204235</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pkrt_q1-25_ril vs sog_q_pkrt_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6304</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Barito Kuala</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.7415140831895454</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -687,6 +1609,656 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.1482475291487077</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6228577150772824</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4095997213905072</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6308</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.09902974921140051</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.944179660809778</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6301</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tanah Laut</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.5299099758154495</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>14.80876324098713</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3098942572561483</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.7535055554907971</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6303</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Banjar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.03788775481255909</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.761445180102199</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7698712134636685</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-6.677521760594272</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6305</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapin</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.08091323801344114</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6306</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.792584558101327</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -724,85 +2296,187 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Kuala</t>
+          <t>Kabupaten Hulu Sungai Tengah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1021837427310617</v>
+        <v>-13.81425819235558</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Kuala</t>
+          <t>Kabupaten Hulu Sungai Tengah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1021837427310617</v>
+        <v>4.882020817119469</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6304</v>
+        <v>6307</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Barito Kuala</t>
+          <t>Kabupaten Hulu Sungai Tengah</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.03315964553975817</v>
+        <v>2.030368241102948</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2263080703893155</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6309</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabalong</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.971094544102494</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_63.xlsx
+++ b/data/output/evaluasi_63.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
